--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/ene-2025.xlsx
@@ -1055,7 +1055,11 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>AMINORTE S A</t>
@@ -1307,7 +1311,11 @@
           <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
@@ -1429,7 +1437,11 @@
           <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>EVENTAIL SPA</t>
@@ -1872,7 +1884,11 @@
           <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -2185,7 +2201,11 @@
           <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
@@ -2242,7 +2262,11 @@
           <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -2494,7 +2518,11 @@
           <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
@@ -2616,7 +2644,11 @@
           <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA NENE SPA</t>
@@ -4441,7 +4473,11 @@
           <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>MALMO S.A.</t>
@@ -5518,7 +5554,11 @@
           <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -5705,7 +5745,11 @@
           <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -6514,7 +6558,11 @@
           <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -6697,7 +6745,11 @@
           <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
@@ -6754,7 +6806,11 @@
           <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
@@ -7510,7 +7566,11 @@
           <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -8144,7 +8204,11 @@
           <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -8270,7 +8334,11 @@
           <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr">
         <is>
           <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
@@ -10424,7 +10492,11 @@
           <t>Hospital  Lonquimay</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I159" t="inlineStr">
         <is>
           <t>COMERCIAL RED OFFICE LIMITADA</t>
@@ -11570,7 +11642,11 @@
           <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I177" t="inlineStr">
         <is>
           <t>COMERCIAL RED OFFICE LIMITADA</t>
@@ -11956,7 +12032,11 @@
           <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I183" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribuidora Colon </t>
@@ -13094,7 +13174,11 @@
           <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I201" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -13350,7 +13434,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I205" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -13411,7 +13499,11 @@
           <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I206" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -14033,7 +14125,11 @@
           <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I216" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA VERGIO SPA</t>
@@ -14411,7 +14507,11 @@
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I222" t="inlineStr">
         <is>
           <t>CHRISTIAN ALBERTO SCHMIDLIN MUÑOZ</t>
@@ -15423,7 +15523,11 @@
           <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I238" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -16118,7 +16222,11 @@
           <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I249" t="inlineStr">
         <is>
           <t>SOCIEDAD DE INVERSIONES MILCON SPA</t>
@@ -16175,7 +16283,11 @@
           <t>I MUNICIPALIDAD DE CONCHALI</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I250" t="inlineStr">
         <is>
           <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
@@ -16414,7 +16526,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -18321,7 +18433,11 @@
           <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr"/>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I284" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -20223,7 +20339,11 @@
           <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr"/>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I314" t="inlineStr">
         <is>
           <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
@@ -20345,7 +20465,11 @@
           <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I316" t="inlineStr">
         <is>
           <t>INVERSIONES CATALUÑA SPA</t>
@@ -21853,7 +21977,11 @@
           <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr"/>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I340" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -21911,7 +22039,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -23950,7 +24078,11 @@
           <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr"/>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I373" t="inlineStr">
         <is>
           <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
@@ -24710,7 +24842,11 @@
           <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr"/>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
       <c r="I385" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -24771,7 +24907,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr"/>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I386" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -24897,7 +25037,11 @@
           <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr"/>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I388" t="inlineStr">
         <is>
           <t>CASTILLA Y ARAGON SPA</t>
@@ -25023,7 +25167,11 @@
           <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr"/>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
       <c r="I390" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -25902,10 +26050,14 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
-        </is>
-      </c>
-      <c r="H404" t="inlineStr"/>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
       <c r="I404" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -25953,7 +26105,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -26096,7 +26248,11 @@
           <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr"/>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I407" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -27368,7 +27524,11 @@
           <t>INSTITUTO NACIONAL DEL TORAX</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I427" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -27685,7 +27845,11 @@
           <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
-      <c r="H432" t="inlineStr"/>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I432" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -28823,7 +28987,11 @@
           <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
-      <c r="H450" t="inlineStr"/>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="I450" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -29757,7 +29925,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -29896,7 +30064,11 @@
           <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
-      <c r="H467" t="inlineStr"/>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I467" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribuidora Colon </t>
@@ -29953,7 +30125,11 @@
           <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
-      <c r="H468" t="inlineStr"/>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I468" t="inlineStr">
         <is>
           <t>LIBRERÍA ATLANTIK LIMITADA</t>
@@ -30262,7 +30438,11 @@
           <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
-      <c r="H473" t="inlineStr"/>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
       <c r="I473" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
@@ -30637,7 +30817,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -31469,7 +31649,11 @@
           <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr"/>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I492" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -31843,7 +32027,11 @@
           <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
-      <c r="H498" t="inlineStr"/>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I498" t="inlineStr">
         <is>
           <t>COMERCIAL Y DISTRIBUIDORA ULAP LIMITADA</t>
@@ -31969,7 +32157,11 @@
           <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
-      <c r="H500" t="inlineStr"/>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="I500" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -32147,7 +32339,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
@@ -32225,7 +32417,11 @@
           <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
-      <c r="H504" t="inlineStr"/>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="I504" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -32412,7 +32608,11 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H507" t="inlineStr"/>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I507" t="inlineStr">
         <is>
           <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
@@ -32599,7 +32799,11 @@
           <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
         </is>
       </c>
-      <c r="H510" t="inlineStr"/>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I510" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -32790,7 +32994,11 @@
           <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr"/>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
       <c r="I513" t="inlineStr">
         <is>
           <t>IMPORTADORA Y COMERCIALIZADORA FERVET ON LINE LIMITADA</t>
@@ -35375,7 +35583,11 @@
           <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
-      <c r="H554" t="inlineStr"/>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="I554" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -35559,7 +35771,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -35688,7 +35900,11 @@
           <t>I MUNICIPALIDAD DE COLINA</t>
         </is>
       </c>
-      <c r="H559" t="inlineStr"/>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I559" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -36514,7 +36730,7 @@
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -36575,7 +36791,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -37855,7 +38071,7 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -38232,7 +38448,11 @@
           <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
-      <c r="H599" t="inlineStr"/>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I599" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
@@ -38782,7 +39002,7 @@
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -38847,7 +39067,7 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -39156,7 +39376,7 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -39415,7 +39635,11 @@
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
-      <c r="H618" t="inlineStr"/>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I618" t="inlineStr">
         <is>
           <t>CHRISTIAN ALBERTO SCHMIDLIN MUÑOZ</t>
@@ -40114,7 +40338,11 @@
           <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
-      <c r="H629" t="inlineStr"/>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
       <c r="I629" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
@@ -40158,7 +40386,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
